--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MARYLAND_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MARYLAND_2020.xlsx
@@ -391,7 +391,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="3">
@@ -409,7 +409,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="4">
@@ -427,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="D4">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="5">
@@ -445,7 +445,7 @@
         <v>1</v>
       </c>
       <c r="D5">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="6">
@@ -481,7 +481,7 @@
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="9">
@@ -553,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="14">
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="D14">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="15">
@@ -643,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="D16">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="17">
@@ -679,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="19">
@@ -733,7 +733,7 @@
         <v>1</v>
       </c>
       <c r="D21">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="22">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="24">
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="D24">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="25">
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="D25">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="26">
@@ -823,7 +823,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="27">
@@ -841,7 +841,7 @@
         <v>1</v>
       </c>
       <c r="D27">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="28">
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="D30">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="31">
@@ -913,7 +913,7 @@
         <v>1</v>
       </c>
       <c r="D31">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="32">
@@ -1003,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="D36">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="37">
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="D40">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="41">
@@ -1129,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="44">
@@ -1165,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="D45">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="46">
@@ -1183,7 +1183,7 @@
         <v>1</v>
       </c>
       <c r="D46">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="47">
@@ -1201,7 +1201,7 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="48">
@@ -1219,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="49">
@@ -1309,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="54">
@@ -1327,7 +1327,7 @@
         <v>10</v>
       </c>
       <c r="D54">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="55">
@@ -1345,7 +1345,7 @@
         <v>10</v>
       </c>
       <c r="D55">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="56">
@@ -1453,7 +1453,7 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="62">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C63">
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="D64">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="65">
@@ -1525,7 +1525,7 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="66">
@@ -1543,7 +1543,7 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="67">
@@ -1561,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="68">
@@ -1597,7 +1597,7 @@
         <v>1</v>
       </c>
       <c r="D69">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="70">
@@ -1615,7 +1615,7 @@
         <v>1</v>
       </c>
       <c r="D70">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="71">
@@ -1633,7 +1633,7 @@
         <v>1</v>
       </c>
       <c r="D71">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="72">
@@ -1669,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="74">
@@ -1723,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="D76">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="77">
@@ -1741,7 +1741,7 @@
         <v>1</v>
       </c>
       <c r="D77">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="78">
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="79">
@@ -1813,7 +1813,7 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="82">
@@ -1831,7 +1831,7 @@
         <v>1</v>
       </c>
       <c r="D82">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="83">
@@ -1867,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="85">
@@ -1921,7 +1921,7 @@
         <v>1</v>
       </c>
       <c r="D87">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="88">
@@ -1975,7 +1975,7 @@
         <v>1</v>
       </c>
       <c r="D90">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="91">
@@ -1993,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="D91">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="92">
@@ -2011,7 +2011,7 @@
         <v>1</v>
       </c>
       <c r="D92">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="93">
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="D94">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="95">
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="D95">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="96">
@@ -2137,7 +2137,7 @@
         <v>1</v>
       </c>
       <c r="D99">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="100">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C101">
@@ -2209,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="104">
@@ -2227,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="D104">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="105">
@@ -2245,7 +2245,7 @@
         <v>11</v>
       </c>
       <c r="D105">
-        <v>0.009909909909909909</v>
+        <v>0.009909909909909908</v>
       </c>
     </row>
     <row r="106">
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="108">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C108">
@@ -2317,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="D109">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="110">
@@ -2353,7 +2353,7 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="112">
@@ -2371,7 +2371,7 @@
         <v>11</v>
       </c>
       <c r="D112">
-        <v>0.009909909909909909</v>
+        <v>0.009909909909909908</v>
       </c>
     </row>
     <row r="113">
@@ -2425,7 +2425,7 @@
         <v>1</v>
       </c>
       <c r="D115">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="116">
@@ -2461,7 +2461,7 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="118">
@@ -2533,7 +2533,7 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="122">
@@ -2551,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="D122">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="123">
@@ -2587,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="125">
@@ -2623,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="D126">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="127">
@@ -2641,7 +2641,7 @@
         <v>1</v>
       </c>
       <c r="D127">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="128">
@@ -2659,7 +2659,7 @@
         <v>1</v>
       </c>
       <c r="D128">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="129">
@@ -2749,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="D133">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="134">
@@ -2821,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="D137">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="138">
@@ -2839,7 +2839,7 @@
         <v>1</v>
       </c>
       <c r="D138">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="139">
@@ -2857,7 +2857,7 @@
         <v>1</v>
       </c>
       <c r="D139">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="140">
@@ -2875,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="D140">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="141">
@@ -2911,7 +2911,7 @@
         <v>1</v>
       </c>
       <c r="D142">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="143">
@@ -2947,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="D144">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="145">
@@ -2983,7 +2983,7 @@
         <v>1</v>
       </c>
       <c r="D146">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="147">
@@ -3001,7 +3001,7 @@
         <v>1</v>
       </c>
       <c r="D147">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="148">
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="D151">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="152">
@@ -3091,7 +3091,7 @@
         <v>1</v>
       </c>
       <c r="D152">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="153">
@@ -3109,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="D153">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="154">
@@ -3145,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="D155">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="156">
@@ -3163,7 +3163,7 @@
         <v>1</v>
       </c>
       <c r="D156">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="157">
@@ -3181,7 +3181,7 @@
         <v>1</v>
       </c>
       <c r="D157">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="158">
@@ -3235,7 +3235,7 @@
         <v>1</v>
       </c>
       <c r="D160">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="161">
@@ -3253,7 +3253,7 @@
         <v>1</v>
       </c>
       <c r="D161">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="162">
@@ -3271,7 +3271,7 @@
         <v>1</v>
       </c>
       <c r="D162">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="163">
@@ -3307,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="D164">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="165">
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="D166">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="167">
@@ -3433,7 +3433,7 @@
         <v>1</v>
       </c>
       <c r="D171">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="172">
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="D172">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="173">
@@ -3505,7 +3505,7 @@
         <v>1</v>
       </c>
       <c r="D175">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="176">
@@ -3523,7 +3523,7 @@
         <v>1</v>
       </c>
       <c r="D176">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="177">
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="D177">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="178">
@@ -3559,7 +3559,7 @@
         <v>1</v>
       </c>
       <c r="D178">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="179">
@@ -3577,7 +3577,7 @@
         <v>1</v>
       </c>
       <c r="D179">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="180">
@@ -3595,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="D180">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="181">
@@ -3613,7 +3613,7 @@
         <v>1</v>
       </c>
       <c r="D181">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="182">
@@ -3649,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="D183">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="184">
@@ -3685,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="D185">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="186">
@@ -3703,7 +3703,7 @@
         <v>1</v>
       </c>
       <c r="D186">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="187">
@@ -3721,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="D187">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="188">
@@ -3739,7 +3739,7 @@
         <v>1</v>
       </c>
       <c r="D188">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="189">
@@ -3793,7 +3793,7 @@
         <v>1</v>
       </c>
       <c r="D191">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="192">
@@ -3811,7 +3811,7 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="193">
@@ -3865,7 +3865,7 @@
         <v>1</v>
       </c>
       <c r="D195">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="196">
@@ -3883,7 +3883,7 @@
         <v>1</v>
       </c>
       <c r="D196">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="197">
@@ -3901,7 +3901,7 @@
         <v>1</v>
       </c>
       <c r="D197">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="198">
@@ -3919,7 +3919,7 @@
         <v>1</v>
       </c>
       <c r="D198">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="199">
@@ -3955,7 +3955,7 @@
         <v>1</v>
       </c>
       <c r="D200">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="201">
@@ -3991,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="D202">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="203">
@@ -4027,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="D204">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="205">
@@ -4099,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="209">
@@ -4117,7 +4117,7 @@
         <v>1</v>
       </c>
       <c r="D209">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="210">
@@ -4171,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="D212">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="213">
@@ -4297,7 +4297,7 @@
         <v>1</v>
       </c>
       <c r="D219">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="220">
@@ -4405,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="D225">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="226">
@@ -4423,7 +4423,7 @@
         <v>1</v>
       </c>
       <c r="D226">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="227">
@@ -4441,7 +4441,7 @@
         <v>1</v>
       </c>
       <c r="D227">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="228">
@@ -4452,14 +4452,14 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>General Zaragoza</t>
+          <t>Gral. Zaragoza</t>
         </is>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="229">
@@ -4495,7 +4495,7 @@
         <v>1</v>
       </c>
       <c r="D230">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="231">
@@ -4513,7 +4513,7 @@
         <v>1</v>
       </c>
       <c r="D231">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="232">
@@ -4567,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="D234">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="235">
@@ -4585,7 +4585,7 @@
         <v>1</v>
       </c>
       <c r="D235">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="236">
@@ -4621,7 +4621,7 @@
         <v>1</v>
       </c>
       <c r="D237">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="238">
@@ -4639,7 +4639,7 @@
         <v>1</v>
       </c>
       <c r="D238">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="239">
@@ -4657,7 +4657,7 @@
         <v>1</v>
       </c>
       <c r="D239">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="240">
@@ -4693,7 +4693,7 @@
         <v>1</v>
       </c>
       <c r="D241">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="242">
@@ -4711,7 +4711,7 @@
         <v>1</v>
       </c>
       <c r="D242">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="243">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C243">
@@ -4747,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="D244">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="245">
@@ -4783,7 +4783,7 @@
         <v>1</v>
       </c>
       <c r="D246">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="247">
@@ -4801,7 +4801,7 @@
         <v>1</v>
       </c>
       <c r="D247">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="248">
@@ -4837,7 +4837,7 @@
         <v>1</v>
       </c>
       <c r="D249">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="250">
@@ -4855,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="D250">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="251">
@@ -4873,7 +4873,7 @@
         <v>1</v>
       </c>
       <c r="D251">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="252">
@@ -4891,7 +4891,7 @@
         <v>1</v>
       </c>
       <c r="D252">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="253">
@@ -4909,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="254">
@@ -4945,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="D255">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="256">
@@ -4963,7 +4963,7 @@
         <v>1</v>
       </c>
       <c r="D256">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="257">
@@ -4999,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="D258">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="259">
@@ -5017,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="D259">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="260">
@@ -5053,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="D261">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="262">
@@ -5071,7 +5071,7 @@
         <v>1</v>
       </c>
       <c r="D262">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="263">
@@ -5089,7 +5089,7 @@
         <v>1</v>
       </c>
       <c r="D263">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="264">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="D264">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="265">
@@ -5143,7 +5143,7 @@
         <v>1</v>
       </c>
       <c r="D266">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="267">
@@ -5197,7 +5197,7 @@
         <v>1</v>
       </c>
       <c r="D269">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="270">
@@ -5251,7 +5251,7 @@
         <v>1</v>
       </c>
       <c r="D272">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="273">
@@ -5341,7 +5341,7 @@
         <v>1</v>
       </c>
       <c r="D277">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="278">
@@ -5359,7 +5359,7 @@
         <v>1</v>
       </c>
       <c r="D278">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="279">
@@ -5377,7 +5377,7 @@
         <v>1</v>
       </c>
       <c r="D279">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="280">
@@ -5431,7 +5431,7 @@
         <v>1</v>
       </c>
       <c r="D282">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="283">
@@ -5467,7 +5467,7 @@
         <v>1</v>
       </c>
       <c r="D284">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="285">
@@ -5485,7 +5485,7 @@
         <v>1</v>
       </c>
       <c r="D285">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="286">
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="D286">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="287">
@@ -5521,7 +5521,7 @@
         <v>10</v>
       </c>
       <c r="D287">
-        <v>0.009009009009009009</v>
+        <v>0.009009009009009007</v>
       </c>
     </row>
     <row r="288">
@@ -5539,7 +5539,7 @@
         <v>1</v>
       </c>
       <c r="D288">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="289">
@@ -5557,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="D289">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="290">
@@ -5575,7 +5575,7 @@
         <v>1</v>
       </c>
       <c r="D290">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="291">
@@ -5593,7 +5593,7 @@
         <v>1</v>
       </c>
       <c r="D291">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="292">
@@ -5611,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="D292">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="293">
@@ -5701,7 +5701,7 @@
         <v>1</v>
       </c>
       <c r="D297">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="298">
@@ -5719,7 +5719,7 @@
         <v>1</v>
       </c>
       <c r="D298">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="299">
@@ -5737,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="D299">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="300">
@@ -5755,7 +5755,7 @@
         <v>1</v>
       </c>
       <c r="D300">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="301">
@@ -5791,7 +5791,7 @@
         <v>1</v>
       </c>
       <c r="D302">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="303">
@@ -5827,7 +5827,7 @@
         <v>1</v>
       </c>
       <c r="D304">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="305">
@@ -5845,7 +5845,7 @@
         <v>1</v>
       </c>
       <c r="D305">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="306">
@@ -5881,7 +5881,7 @@
         <v>1</v>
       </c>
       <c r="D307">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="308">
@@ -5917,7 +5917,7 @@
         <v>1</v>
       </c>
       <c r="D309">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="310">
@@ -5935,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="D310">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="311">
@@ -5971,7 +5971,7 @@
         <v>1</v>
       </c>
       <c r="D312">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="313">
@@ -6007,7 +6007,7 @@
         <v>1</v>
       </c>
       <c r="D314">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="315">
@@ -6043,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="317">
@@ -6054,14 +6054,14 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C317">
         <v>1</v>
       </c>
       <c r="D317">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="318">
@@ -6079,7 +6079,7 @@
         <v>1</v>
       </c>
       <c r="D318">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="319">
@@ -6133,7 +6133,7 @@
         <v>1</v>
       </c>
       <c r="D321">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="322">
@@ -6151,7 +6151,7 @@
         <v>1</v>
       </c>
       <c r="D322">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="323">
@@ -6187,7 +6187,7 @@
         <v>1</v>
       </c>
       <c r="D324">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="325">
@@ -6205,7 +6205,7 @@
         <v>1</v>
       </c>
       <c r="D325">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="326">
@@ -6223,7 +6223,7 @@
         <v>1</v>
       </c>
       <c r="D326">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="327">
@@ -6241,7 +6241,7 @@
         <v>1</v>
       </c>
       <c r="D327">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="328">
@@ -6295,7 +6295,7 @@
         <v>1</v>
       </c>
       <c r="D330">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="331">
@@ -6331,7 +6331,7 @@
         <v>1</v>
       </c>
       <c r="D332">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="333">
@@ -6367,7 +6367,7 @@
         <v>1</v>
       </c>
       <c r="D334">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="335">
@@ -6403,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="D336">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="337">
@@ -6511,7 +6511,7 @@
         <v>1</v>
       </c>
       <c r="D342">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="343">
@@ -6529,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="D343">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="344">
@@ -6583,7 +6583,7 @@
         <v>1</v>
       </c>
       <c r="D346">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="347">
@@ -6601,7 +6601,7 @@
         <v>1</v>
       </c>
       <c r="D347">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="348">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C348">
@@ -6637,7 +6637,7 @@
         <v>1</v>
       </c>
       <c r="D349">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="350">
@@ -6673,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="D351">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="352">
@@ -6727,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="D354">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="355">
@@ -6745,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="D355">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="356">
@@ -6799,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="D358">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="359">
@@ -6817,7 +6817,7 @@
         <v>1</v>
       </c>
       <c r="D359">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="360">
@@ -6853,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="D361">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="362">
@@ -6871,7 +6871,7 @@
         <v>1</v>
       </c>
       <c r="D362">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="363">
@@ -6907,7 +6907,7 @@
         <v>1</v>
       </c>
       <c r="D364">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="365">
@@ -6943,7 +6943,7 @@
         <v>1</v>
       </c>
       <c r="D366">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="367">
@@ -6979,7 +6979,7 @@
         <v>1</v>
       </c>
       <c r="D368">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="369">
@@ -6997,7 +6997,7 @@
         <v>1</v>
       </c>
       <c r="D369">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="370">
@@ -7015,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="D370">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="371">
@@ -7033,7 +7033,7 @@
         <v>1</v>
       </c>
       <c r="D371">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="372">
@@ -7051,7 +7051,7 @@
         <v>1</v>
       </c>
       <c r="D372">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="373">
@@ -7069,7 +7069,7 @@
         <v>1</v>
       </c>
       <c r="D373">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="374">
@@ -7105,7 +7105,7 @@
         <v>1</v>
       </c>
       <c r="D375">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="376">
@@ -7141,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="D377">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="378">
@@ -7159,7 +7159,7 @@
         <v>1</v>
       </c>
       <c r="D378">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="379">
@@ -7195,7 +7195,7 @@
         <v>1</v>
       </c>
       <c r="D380">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="381">
@@ -7213,7 +7213,7 @@
         <v>1</v>
       </c>
       <c r="D381">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="382">
@@ -7249,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="D383">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="384">
@@ -7267,7 +7267,7 @@
         <v>1</v>
       </c>
       <c r="D384">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="385">
@@ -7285,7 +7285,7 @@
         <v>1</v>
       </c>
       <c r="D385">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="386">
@@ -7303,7 +7303,7 @@
         <v>1</v>
       </c>
       <c r="D386">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="387">
@@ -7339,7 +7339,7 @@
         <v>1</v>
       </c>
       <c r="D388">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="389">
@@ -7357,7 +7357,7 @@
         <v>1</v>
       </c>
       <c r="D389">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="390">
@@ -7411,7 +7411,7 @@
         <v>1</v>
       </c>
       <c r="D392">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="393">
@@ -7447,7 +7447,7 @@
         <v>1</v>
       </c>
       <c r="D394">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="395">
@@ -7465,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="D395">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="396">
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="D396">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="397">
@@ -7519,7 +7519,7 @@
         <v>1</v>
       </c>
       <c r="D398">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="399">
@@ -7537,7 +7537,7 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="400">
@@ -7573,7 +7573,7 @@
         <v>1</v>
       </c>
       <c r="D401">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="402">
@@ -7591,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="D402">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="403">
@@ -7609,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="D403">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="404">
@@ -7645,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="D405">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="406">
@@ -7681,7 +7681,7 @@
         <v>1</v>
       </c>
       <c r="D407">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="408">
@@ -7771,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="D412">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="413">
@@ -7789,7 +7789,7 @@
         <v>1</v>
       </c>
       <c r="D413">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="414">
@@ -7807,7 +7807,7 @@
         <v>1</v>
       </c>
       <c r="D414">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="415">
@@ -7843,7 +7843,7 @@
         <v>1</v>
       </c>
       <c r="D416">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="417">
@@ -7861,7 +7861,7 @@
         <v>1</v>
       </c>
       <c r="D417">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="418">
@@ -7879,7 +7879,7 @@
         <v>1</v>
       </c>
       <c r="D418">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="419">
@@ -7897,7 +7897,7 @@
         <v>1</v>
       </c>
       <c r="D419">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="420">
@@ -7915,7 +7915,7 @@
         <v>1</v>
       </c>
       <c r="D420">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="421">
@@ -7951,7 +7951,7 @@
         <v>1</v>
       </c>
       <c r="D422">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="423">
@@ -7969,7 +7969,7 @@
         <v>1</v>
       </c>
       <c r="D423">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="424">
@@ -8023,7 +8023,7 @@
         <v>1</v>
       </c>
       <c r="D426">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="427">
@@ -8059,7 +8059,7 @@
         <v>1</v>
       </c>
       <c r="D428">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="429">
@@ -8095,7 +8095,7 @@
         <v>1</v>
       </c>
       <c r="D430">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="431">
@@ -8113,7 +8113,7 @@
         <v>1</v>
       </c>
       <c r="D431">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="432">
@@ -8131,7 +8131,7 @@
         <v>1</v>
       </c>
       <c r="D432">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="433">
@@ -8167,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="D434">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="435">
@@ -8203,7 +8203,7 @@
         <v>1</v>
       </c>
       <c r="D436">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="437">
@@ -8221,7 +8221,7 @@
         <v>1</v>
       </c>
       <c r="D437">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="438">
@@ -8239,7 +8239,7 @@
         <v>1</v>
       </c>
       <c r="D438">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="439">
@@ -8257,7 +8257,7 @@
         <v>1</v>
       </c>
       <c r="D439">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="440">
@@ -8275,7 +8275,7 @@
         <v>1</v>
       </c>
       <c r="D440">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="441">
@@ -8293,7 +8293,7 @@
         <v>1</v>
       </c>
       <c r="D441">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="442">
@@ -8311,7 +8311,7 @@
         <v>1</v>
       </c>
       <c r="D442">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="443">
@@ -8329,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="D443">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="444">
@@ -8347,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="D444">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="445">
@@ -8383,7 +8383,7 @@
         <v>1</v>
       </c>
       <c r="D446">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="447">
@@ -8419,7 +8419,7 @@
         <v>1</v>
       </c>
       <c r="D448">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="449">
@@ -8437,7 +8437,7 @@
         <v>1</v>
       </c>
       <c r="D449">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="450">
@@ -8473,7 +8473,7 @@
         <v>1</v>
       </c>
       <c r="D451">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="452">
@@ -8509,7 +8509,7 @@
         <v>1</v>
       </c>
       <c r="D453">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="454">
@@ -8527,7 +8527,7 @@
         <v>1</v>
       </c>
       <c r="D454">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="455">
@@ -8563,7 +8563,7 @@
         <v>1</v>
       </c>
       <c r="D456">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="457">
@@ -8581,7 +8581,7 @@
         <v>1</v>
       </c>
       <c r="D457">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="458">
@@ -8599,7 +8599,7 @@
         <v>1</v>
       </c>
       <c r="D458">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="459">
@@ -8617,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="D459">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="460">
@@ -8653,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="D461">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="462">
@@ -8671,7 +8671,7 @@
         <v>1</v>
       </c>
       <c r="D462">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="463">
@@ -8689,7 +8689,7 @@
         <v>1</v>
       </c>
       <c r="D463">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="464">
@@ -8707,7 +8707,7 @@
         <v>1</v>
       </c>
       <c r="D464">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="465">
@@ -8725,7 +8725,7 @@
         <v>1</v>
       </c>
       <c r="D465">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
     <row r="466">
@@ -8743,7 +8743,7 @@
         <v>1</v>
       </c>
       <c r="D466">
-        <v>0.0009009009009009009</v>
+        <v>0.0009009009009009008</v>
       </c>
     </row>
   </sheetData>
